--- a/output/yearly_surface_area_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_93_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497643121504</v>
+        <v>10.84497637761287</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907228687265</v>
+        <v>37.78907210009712</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.956844158742146</v>
+        <v>5.585162689460105</v>
       </c>
       <c r="C2" t="n">
-        <v>10.90230825566083</v>
+        <v>5.929756133650734</v>
       </c>
       <c r="D2" t="n">
-        <v>20.59903033050658</v>
+        <v>36.37964292856981</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.34471661737765</v>
+        <v>18.75628988963531</v>
       </c>
       <c r="C3" t="n">
-        <v>26.44337441388784</v>
+        <v>21.80952524984289</v>
       </c>
       <c r="D3" t="n">
-        <v>80.62112147274807</v>
+        <v>74.38702355078082</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.68532631748906</v>
+        <v>36.84597308808704</v>
       </c>
       <c r="C4" t="n">
-        <v>71.85411447382405</v>
+        <v>68.9314515582813</v>
       </c>
       <c r="D4" t="n">
-        <v>99.4343527292297</v>
+        <v>92.82326368883167</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.80419990516094</v>
+        <v>45.01313223971626</v>
       </c>
       <c r="C5" t="n">
-        <v>106.7405191442345</v>
+        <v>96.92304210176638</v>
       </c>
       <c r="D5" t="n">
-        <v>69.99861131279759</v>
+        <v>64.59899893944014</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.36611944488861</v>
+        <v>42.02272873258048</v>
       </c>
       <c r="C6" t="n">
-        <v>108.4782125807513</v>
+        <v>93.30333831620838</v>
       </c>
       <c r="D6" t="n">
-        <v>46.41015922285948</v>
+        <v>44.67933802027235</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64954143177966</v>
+        <v>27.90716024091983</v>
       </c>
       <c r="C7" t="n">
-        <v>101.0287110009265</v>
+        <v>80.72715022480672</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>14.6034971006713</v>
       </c>
       <c r="C8" t="n">
-        <v>74.18576527141022</v>
+        <v>56.66156875060466</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4874963073167</v>
+        <v>36.27655941962388</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.688197807164243</v>
+        <v>7.714561711917029</v>
       </c>
       <c r="C21" t="n">
-        <v>94.18042313776198</v>
+        <v>96.43202139896286</v>
       </c>
       <c r="D21" t="n">
-        <v>8.649222533059774</v>
+        <v>8.678881925906657</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.451465075233291</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C2" t="n">
-        <v>12.64196518758618</v>
+        <v>7.691011515069513</v>
       </c>
       <c r="D2" t="n">
-        <v>17.37987960828128</v>
+        <v>30.26728172192916</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90922154731956</v>
+        <v>18.71211124294421</v>
       </c>
       <c r="C3" t="n">
-        <v>34.49370558871168</v>
+        <v>22.35439522569988</v>
       </c>
       <c r="D3" t="n">
-        <v>78.24529202847079</v>
+        <v>84.00815105239957</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.97512181669111</v>
+        <v>36.38651516249953</v>
       </c>
       <c r="C4" t="n">
-        <v>68.17845106912399</v>
+        <v>60.83988697987908</v>
       </c>
       <c r="D4" t="n">
-        <v>114.3922607511341</v>
+        <v>105.5221702432642</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.52854978444584</v>
+        <v>49.70097752749479</v>
       </c>
       <c r="C5" t="n">
-        <v>119.3068897585937</v>
+        <v>111.9928693619549</v>
       </c>
       <c r="D5" t="n">
-        <v>85.80474935117124</v>
+        <v>81.2150788338174</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.81896717845365</v>
+        <v>50.95859633663495</v>
       </c>
       <c r="C6" t="n">
-        <v>136.372610101516</v>
+        <v>121.6807557074624</v>
       </c>
       <c r="D6" t="n">
-        <v>56.27181491201868</v>
+        <v>53.05168244208915</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.29128563518759</v>
+        <v>38.74663664350886</v>
       </c>
       <c r="C7" t="n">
-        <v>128.1573453123786</v>
+        <v>107.4365782665454</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>42.81892612072463</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.86213871524472</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="C8" t="n">
-        <v>102.1410311498382</v>
+        <v>80.69475255056658</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.53906160508951</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>66.67343183851361</v>
+        <v>53.0281204971872</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>36.58482819875739</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.869289685519528</v>
+        <v>7.901210177974066</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3007659117539</v>
+        <v>105.6786861304031</v>
       </c>
       <c r="D21" t="n">
-        <v>9.836612106899411</v>
+        <v>9.876512722467583</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.896196785257096</v>
+        <v>7.801949005649402</v>
       </c>
       <c r="C2" t="n">
-        <v>9.8341667534403</v>
+        <v>7.865762606425444</v>
       </c>
       <c r="D2" t="n">
-        <v>20.32414097331747</v>
+        <v>34.53690248769854</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.72822011683965</v>
+        <v>20.09146676741098</v>
       </c>
       <c r="C3" t="n">
-        <v>41.14013754646259</v>
+        <v>25.82978209873358</v>
       </c>
       <c r="D3" t="n">
-        <v>74.22012644105887</v>
+        <v>87.11047379781949</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.01791780505048</v>
+        <v>35.37826027023806</v>
       </c>
       <c r="C4" t="n">
-        <v>76.24449020721578</v>
+        <v>57.75130870231862</v>
       </c>
       <c r="D4" t="n">
-        <v>124.5896741551457</v>
+        <v>118.6422465628185</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.70035563268903</v>
+        <v>51.56629816556373</v>
       </c>
       <c r="C5" t="n">
-        <v>120.656792851933</v>
+        <v>111.8701508989241</v>
       </c>
       <c r="D5" t="n">
-        <v>101.6845184673634</v>
+        <v>97.43845964649596</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.97747052719389</v>
+        <v>57.9623844587317</v>
       </c>
       <c r="C6" t="n">
-        <v>158.2695108970368</v>
+        <v>145.5499876408151</v>
       </c>
       <c r="D6" t="n">
-        <v>67.66303352439442</v>
+        <v>63.35610634586367</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.79518424937346</v>
+        <v>48.80758711663017</v>
       </c>
       <c r="C7" t="n">
-        <v>158.819289611415</v>
+        <v>138.3979556153771</v>
       </c>
       <c r="D7" t="n">
-        <v>47.4301950875719</v>
+        <v>47.66974152740813</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.45595720759379</v>
+        <v>30.45872252425729</v>
       </c>
       <c r="C8" t="n">
-        <v>131.0142311317368</v>
+        <v>107.5651872158018</v>
       </c>
       <c r="D8" t="n">
-        <v>40.88979188187965</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>15.64218617176442</v>
       </c>
       <c r="C9" t="n">
-        <v>92.2999921624681</v>
+        <v>73.66249374504666</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>37.82968428774233</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>57.36842709766236</v>
+        <v>48.54251523648354</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>37.13853390395258</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.034849920197562</v>
+        <v>8.072902895865148</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4791864027165</v>
+        <v>114.0297534040952</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04791864027165</v>
+        <v>11.10024148181458</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.164794745593221</v>
+        <v>7.072510461394022</v>
       </c>
       <c r="C2" t="n">
-        <v>6.686683613625026</v>
+        <v>5.285729639664827</v>
       </c>
       <c r="D2" t="n">
-        <v>16.82911914619882</v>
+        <v>28.02202472231671</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.44275251908209</v>
+        <v>24.60259746842507</v>
       </c>
       <c r="C3" t="n">
-        <v>57.21625620350412</v>
+        <v>38.57286729985718</v>
       </c>
       <c r="D3" t="n">
-        <v>83.11966938005621</v>
+        <v>95.23934478898308</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.95187866695868</v>
+        <v>24.77243982125977</v>
       </c>
       <c r="C4" t="n">
-        <v>102.6760836486527</v>
+        <v>88.54775243683682</v>
       </c>
       <c r="D4" t="n">
-        <v>117.876483353506</v>
+        <v>113.1159887356133</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.40963513904496</v>
+        <v>32.64311116620645</v>
       </c>
       <c r="C5" t="n">
-        <v>94.56684761157402</v>
+        <v>86.95830290366123</v>
       </c>
       <c r="D5" t="n">
-        <v>67.76513528563609</v>
+        <v>64.96715432853269</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.81389420901639</v>
+        <v>30.30949687321178</v>
       </c>
       <c r="C6" t="n">
-        <v>104.5738019609618</v>
+        <v>91.12974889900595</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>31.396291581813</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>92.10560611702725</v>
+        <v>75.63678837828701</v>
       </c>
       <c r="D7" t="n">
-        <v>28.7455727803466</v>
+        <v>28.56591295046944</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>68.01057221169779</v>
+        <v>54.24156065963627</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>43.70937128847648</v>
+        <v>37.05312185368311</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.21366114662731</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C2" t="n">
-        <v>3.126866438026091</v>
+        <v>2.510328879759094</v>
       </c>
       <c r="D2" t="n">
-        <v>11.81140662979338</v>
+        <v>19.6074651492173</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.08227118517426</v>
+        <v>25.22109852210056</v>
       </c>
       <c r="C3" t="n">
-        <v>41.92062697133881</v>
+        <v>29.71750300755095</v>
       </c>
       <c r="D3" t="n">
-        <v>78.47109400044756</v>
+        <v>96.9721294869787</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.92407093607028</v>
+        <v>34.68907338185679</v>
       </c>
       <c r="C4" t="n">
-        <v>126.1594887342364</v>
+        <v>95.73316388421922</v>
       </c>
       <c r="D4" t="n">
-        <v>131.6346956808208</v>
+        <v>132.502560651375</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.13398501832986</v>
+        <v>36.47192721276901</v>
       </c>
       <c r="C5" t="n">
-        <v>139.6045235438964</v>
+        <v>124.5101525911018</v>
       </c>
       <c r="D5" t="n">
-        <v>86.83558444063038</v>
+        <v>83.27674901273571</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.40887437551896</v>
+        <v>36.14598697495907</v>
       </c>
       <c r="C6" t="n">
-        <v>127.3562391857132</v>
+        <v>114.0329410913798</v>
       </c>
       <c r="D6" t="n">
-        <v>39.40637110076273</v>
+        <v>39.1246095096439</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>117.5574153496258</v>
+        <v>99.2919993121139</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>87.62098260402782</v>
+        <v>70.68092596724911</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>49.92187076095029</v>
+        <v>43.59843379789659</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.560218086226434</v>
+        <v>6.072109550766522</v>
       </c>
       <c r="C2" t="n">
-        <v>7.683157533435538</v>
+        <v>8.153414683769761</v>
       </c>
       <c r="D2" t="n">
-        <v>15.16014804897925</v>
+        <v>16.91943993498953</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.35024725070463</v>
+        <v>19.777307502052</v>
       </c>
       <c r="C3" t="n">
-        <v>26.22248118043231</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D3" t="n">
-        <v>71.02944640225672</v>
+        <v>90.45332473077987</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.94356702143497</v>
+        <v>41.74685762768712</v>
       </c>
       <c r="C4" t="n">
-        <v>115.119735799981</v>
+        <v>85.254970636793</v>
       </c>
       <c r="D4" t="n">
-        <v>139.4454804158084</v>
+        <v>149.1451477337669</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.34353924769093</v>
+        <v>43.95775345765094</v>
       </c>
       <c r="C5" t="n">
-        <v>185.1330733283423</v>
+        <v>150.5019230610361</v>
       </c>
       <c r="D5" t="n">
-        <v>109.7348496421873</v>
+        <v>108.7285582453343</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.7220929509027</v>
+        <v>42.46549694719579</v>
       </c>
       <c r="C6" t="n">
-        <v>173.1626235704609</v>
+        <v>155.5323982975967</v>
       </c>
       <c r="D6" t="n">
-        <v>53.69570893607505</v>
+        <v>53.53470231257858</v>
       </c>
     </row>
     <row r="7">
@@ -2405,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.76931465169778</v>
+        <v>29.22466566001905</v>
       </c>
       <c r="C7" t="n">
-        <v>149.6566382876795</v>
+        <v>130.2533766609455</v>
       </c>
       <c r="D7" t="n">
         <v>34.7941203862112</v>
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>13.60211444233956</v>
       </c>
       <c r="C8" t="n">
-        <v>118.9976392317559</v>
+        <v>99.80447161373074</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>75.10468112258522</v>
+        <v>64.12186955517615</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>44.27191272300992</v>
+        <v>41.14013754646259</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.68998870963626</v>
+        <v>3.536255230697011</v>
       </c>
       <c r="C2" t="n">
-        <v>3.605959317698535</v>
+        <v>3.672718161587317</v>
       </c>
       <c r="D2" t="n">
-        <v>10.57931326096363</v>
+        <v>11.70537787773472</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.46805697521425</v>
+        <v>21.6082669704723</v>
       </c>
       <c r="C3" t="n">
-        <v>29.52115346670159</v>
+        <v>25.85432579133975</v>
       </c>
       <c r="D3" t="n">
-        <v>69.92988897350031</v>
+        <v>87.62589134254907</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.10421379203296</v>
+        <v>46.14999608123406</v>
       </c>
       <c r="C4" t="n">
-        <v>108.4448331588069</v>
+        <v>79.8435772909846</v>
       </c>
       <c r="D4" t="n">
-        <v>146.3501120197763</v>
+        <v>160.0189853060046</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.28249096357838</v>
+        <v>46.04396732917541</v>
       </c>
       <c r="C5" t="n">
-        <v>221.8013500819607</v>
+        <v>174.284761196415</v>
       </c>
       <c r="D5" t="n">
-        <v>115.5271610972434</v>
+        <v>118.5705789804085</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.36233132279187</v>
+        <v>35.783722072092</v>
       </c>
       <c r="C6" t="n">
-        <v>205.605458205001</v>
+        <v>189.5047958553534</v>
       </c>
       <c r="D6" t="n">
-        <v>52.5284109157256</v>
+        <v>52.68941753922207</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.26435217434965</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>157.4418975823567</v>
+        <v>135.104192067629</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>91.45961612763286</v>
+        <v>79.52647278251287</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.806816686441631</v>
+        <v>3.87201294554942</v>
       </c>
       <c r="C2" t="n">
-        <v>7.530986639277282</v>
+        <v>4.318708150981719</v>
       </c>
       <c r="D2" t="n">
-        <v>9.146943360467532</v>
+        <v>11.27340888786612</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.52495728433156</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C3" t="n">
-        <v>21.66226309420587</v>
+        <v>19.90002596508285</v>
       </c>
       <c r="D3" t="n">
-        <v>63.58289006554468</v>
+        <v>77.77896186895356</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.76863600362979</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="C4" t="n">
-        <v>91.27897455005143</v>
+        <v>72.12213159708342</v>
       </c>
       <c r="D4" t="n">
-        <v>147.3456041918825</v>
+        <v>166.2089045812808</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.75635630956011</v>
+        <v>56.47503668679778</v>
       </c>
       <c r="C5" t="n">
-        <v>213.333776132832</v>
+        <v>162.7737693641212</v>
       </c>
       <c r="D5" t="n">
-        <v>135.8984259603648</v>
+        <v>143.9978445204009</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.82147045320988</v>
+        <v>46.81267578160067</v>
       </c>
       <c r="C6" t="n">
-        <v>274.5162930614932</v>
+        <v>231.1652596850668</v>
       </c>
       <c r="D6" t="n">
-        <v>70.23913950033806</v>
+        <v>72.89574878802993</v>
       </c>
     </row>
     <row r="7">
@@ -3027,10 +3027,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>217.088961101576</v>
+        <v>198.1049057445554</v>
       </c>
       <c r="D7" t="n">
         <v>40.3036885024443</v>
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>139.5259837275567</v>
+        <v>121.5010958775852</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>63.01249464937726</v>
+        <v>57.02187015806322</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.02829075697391</v>
+        <v>2.704714925199963</v>
       </c>
       <c r="C2" t="n">
-        <v>5.213080309550564</v>
+        <v>2.649737053762141</v>
       </c>
       <c r="D2" t="n">
-        <v>8.498989875664638</v>
+        <v>8.718901361415924</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59091430696534</v>
+        <v>15.55579237379071</v>
       </c>
       <c r="C3" t="n">
-        <v>25.314364554004</v>
+        <v>18.83482970597506</v>
       </c>
       <c r="D3" t="n">
-        <v>57.98201941281663</v>
+        <v>70.97545027852316</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.08020987877453</v>
+        <v>40.08770400751001</v>
       </c>
       <c r="C4" t="n">
-        <v>77.9036438273929</v>
+        <v>63.58387181324892</v>
       </c>
       <c r="D4" t="n">
-        <v>148.0986046810398</v>
+        <v>167.5872783580433</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.12513359345841</v>
+        <v>62.14462967882311</v>
       </c>
       <c r="C5" t="n">
-        <v>201.6018910670826</v>
+        <v>156.6133025199724</v>
       </c>
       <c r="D5" t="n">
-        <v>148.6366024229671</v>
+        <v>162.601963515878</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.50953672516665</v>
+        <v>55.6680400739069</v>
       </c>
       <c r="C6" t="n">
-        <v>309.2132204249839</v>
+        <v>252.176624051357</v>
       </c>
       <c r="D6" t="n">
-        <v>84.60898064739862</v>
+        <v>87.54735152620934</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>278.772169359403</v>
+        <v>248.7689777699162</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>180.9999154934632</v>
+        <v>159.5536368941916</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>71.22186895228909</v>
+        <v>68.11561921605218</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
         <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.768929436603505</v>
+        <v>4.41982816451914</v>
       </c>
       <c r="C2" t="n">
-        <v>6.558074664368693</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33485808260617</v>
+        <v>18.86330038939822</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.891108120286615</v>
+        <v>12.45837836689202</v>
       </c>
       <c r="C3" t="n">
-        <v>22.78145547704723</v>
+        <v>14.8194815956056</v>
       </c>
       <c r="D3" t="n">
-        <v>52.41060119121597</v>
+        <v>63.49453277216247</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.3497485290859</v>
+        <v>34.94432778496097</v>
       </c>
       <c r="C4" t="n">
-        <v>71.17769030559801</v>
+        <v>55.93900244027901</v>
       </c>
       <c r="D4" t="n">
-        <v>143.9762460709075</v>
+        <v>163.3117671060484</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.63425974133501</v>
+        <v>62.02191121579226</v>
       </c>
       <c r="C5" t="n">
-        <v>176.5182372235765</v>
+        <v>139.1627370769854</v>
       </c>
       <c r="D5" t="n">
-        <v>162.4056139750286</v>
+        <v>180.6415775814131</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.80766923208819</v>
+        <v>66.61649047166733</v>
       </c>
       <c r="C6" t="n">
-        <v>314.8082005914865</v>
+        <v>251.8143591484899</v>
       </c>
       <c r="D6" t="n">
-        <v>103.3662522847382</v>
+        <v>110.4505437185832</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.30262463928205</v>
+        <v>35.2133266559246</v>
       </c>
       <c r="C7" t="n">
-        <v>348.8993896214569</v>
+        <v>296.9776987869558</v>
       </c>
       <c r="D7" t="n">
-        <v>53.95783557310894</v>
+        <v>55.81432048183967</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>252.0146356801562</v>
+        <v>228.8159374288041</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>126.579676751654</v>
+        <v>116.7062400900438</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.131595250098078</v>
+        <v>4.504258467084366</v>
       </c>
       <c r="C2" t="n">
-        <v>7.979645340118075</v>
+        <v>4.430627389265855</v>
       </c>
       <c r="D2" t="n">
-        <v>6.135923151542564</v>
+        <v>8.933904108645974</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.724349879284899</v>
+        <v>3.126866438026091</v>
       </c>
       <c r="C2" t="n">
-        <v>3.776783418237479</v>
+        <v>3.691371367968007</v>
       </c>
       <c r="D2" t="n">
-        <v>7.689048019661019</v>
+        <v>13.88387603345839</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.71010668980671</v>
+        <v>16.96950906790612</v>
       </c>
       <c r="C3" t="n">
-        <v>27.02751429791469</v>
+        <v>20.43016972537612</v>
       </c>
       <c r="D3" t="n">
-        <v>56.9266406307513</v>
+        <v>71.21106972754238</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.74685762768712</v>
+        <v>47.36245449597887</v>
       </c>
       <c r="C4" t="n">
-        <v>103.0844906936193</v>
+        <v>79.66489920881168</v>
       </c>
       <c r="D4" t="n">
-        <v>148.8005542895763</v>
+        <v>167.446888436336</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.14027641518284</v>
+        <v>39.80986940720817</v>
       </c>
       <c r="C5" t="n">
-        <v>265.9063656952487</v>
+        <v>211.0512127204581</v>
       </c>
       <c r="D5" t="n">
-        <v>147.8021168743573</v>
+        <v>164.7863521578271</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.79752329321368</v>
+        <v>21.85664913964674</v>
       </c>
       <c r="C6" t="n">
-        <v>288.4031143380643</v>
+        <v>247.4269286582109</v>
       </c>
       <c r="D6" t="n">
-        <v>81.54985480096556</v>
+        <v>86.09829191474104</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>177.204478868845</v>
+        <v>160.915320959982</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>93.29548433457438</v>
+        <v>85.95201150680825</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>25.45180923259856</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
         <v>19.07535789351553</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.671556487433824</v>
+        <v>6.404922022506191</v>
       </c>
       <c r="C2" t="n">
-        <v>5.456553740203772</v>
+        <v>5.087416603406972</v>
       </c>
       <c r="D2" t="n">
-        <v>19.34337501677491</v>
+        <v>8.727737090754145</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.90230825566083</v>
+        <v>9.572040116406402</v>
       </c>
       <c r="C3" t="n">
-        <v>20.10619298297468</v>
+        <v>11.33918598405066</v>
       </c>
       <c r="D3" t="n">
-        <v>8.290859362364314</v>
+        <v>10.64214511403542</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39869823323956</v>
+        <v>13.39893532535591</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14612604460713</v>
+        <v>70.14736729156917</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576317439204655</v>
+        <v>1.576345332394813</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.868486865359933</v>
+        <v>4.314781160164732</v>
       </c>
       <c r="C2" t="n">
-        <v>3.662900684544849</v>
+        <v>3.531346492175777</v>
       </c>
       <c r="D2" t="n">
-        <v>23.52365674145782</v>
+        <v>17.93358531347648</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12029730373262</v>
+        <v>17.31802950291373</v>
       </c>
       <c r="C3" t="n">
-        <v>20.83759502263855</v>
+        <v>16.74861583445059</v>
       </c>
       <c r="D3" t="n">
-        <v>22.53601855098553</v>
+        <v>15.39871274111122</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.74995743505333</v>
+        <v>11.23119373658351</v>
       </c>
       <c r="C4" t="n">
-        <v>31.17932533917445</v>
+        <v>18.0975371800857</v>
       </c>
       <c r="D4" t="n">
-        <v>19.41209735607218</v>
+        <v>20.65008121112741</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44172543616915</v>
+        <v>15.44543456152856</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14857348599629</v>
+        <v>86.16926650115936</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250889565509294</v>
+        <v>3.251670434006014</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.495422737746145</v>
+        <v>5.634250074672444</v>
       </c>
       <c r="C2" t="n">
-        <v>5.552765015219959</v>
+        <v>4.482660017590937</v>
       </c>
       <c r="D2" t="n">
-        <v>26.28236779039136</v>
+        <v>27.07463818771854</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.54244881655876</v>
+        <v>16.00248757922301</v>
       </c>
       <c r="C3" t="n">
-        <v>16.84188186635403</v>
+        <v>15.06491852166731</v>
       </c>
       <c r="D3" t="n">
-        <v>36.12340677776139</v>
+        <v>26.16848505669873</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.25367612278995</v>
+        <v>24.14706653365455</v>
       </c>
       <c r="C4" t="n">
-        <v>43.54640116957152</v>
+        <v>31.95785126864217</v>
       </c>
       <c r="D4" t="n">
-        <v>26.34225440035042</v>
+        <v>23.53445596620454</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.31464229144449</v>
+        <v>10.35743827980385</v>
       </c>
       <c r="C5" t="n">
-        <v>35.12202411942965</v>
+        <v>21.64753687864217</v>
       </c>
       <c r="D5" t="n">
-        <v>29.42788743479815</v>
+        <v>30.23782929080177</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73531522525606</v>
+        <v>16.74500217290594</v>
       </c>
       <c r="C21" t="n">
-        <v>102.085422874062</v>
+        <v>102.1445132547262</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020594567576818</v>
+        <v>5.023500651871783</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.005350706877739</v>
+        <v>5.858088551240718</v>
       </c>
       <c r="C2" t="n">
-        <v>7.94724766587793</v>
+        <v>7.099017649408686</v>
       </c>
       <c r="D2" t="n">
-        <v>22.21400530399258</v>
+        <v>31.34229545807942</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.91903902436203</v>
+        <v>17.81381209355838</v>
       </c>
       <c r="C3" t="n">
-        <v>19.55150553007523</v>
+        <v>16.4344565690916</v>
       </c>
       <c r="D3" t="n">
-        <v>48.0614588614026</v>
+        <v>40.92415305152829</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.1162725019244</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7678752401038</v>
+        <v>35.23787034853076</v>
       </c>
       <c r="D4" t="n">
-        <v>37.86699070050372</v>
+        <v>30.70710469343173</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.99743997198154</v>
+        <v>23.53740120931728</v>
       </c>
       <c r="C5" t="n">
-        <v>59.24847395129502</v>
+        <v>42.21515128261285</v>
       </c>
       <c r="D5" t="n">
-        <v>31.90680038802134</v>
+        <v>32.05406254365837</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.70694046251572</v>
+        <v>9.982410656781569</v>
       </c>
       <c r="C6" t="n">
-        <v>35.09944392223197</v>
+        <v>23.78872862160447</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06152504571947</v>
+        <v>18.07922455409803</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8299491077889</v>
+        <v>117.9454173291157</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880580969797893</v>
+        <v>6.887323639656394</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.873796514508666</v>
+        <v>5.821763886183585</v>
       </c>
       <c r="C2" t="n">
-        <v>9.395325529641976</v>
+        <v>9.053677328564085</v>
       </c>
       <c r="D2" t="n">
-        <v>35.38022376564656</v>
+        <v>29.25411809114646</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50808764691012</v>
+        <v>17.09222753093697</v>
       </c>
       <c r="C3" t="n">
-        <v>24.46515278983052</v>
+        <v>21.57881453934489</v>
       </c>
       <c r="D3" t="n">
-        <v>51.04597188231291</v>
+        <v>52.34187885191869</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.42860714059513</v>
+        <v>22.97289627937536</v>
       </c>
       <c r="C4" t="n">
-        <v>38.35197406640165</v>
+        <v>32.34073287329843</v>
       </c>
       <c r="D4" t="n">
-        <v>45.90750439828511</v>
+        <v>37.79041437957247</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.00310947402876</v>
+        <v>20.32217747790898</v>
       </c>
       <c r="C5" t="n">
-        <v>52.10625940289948</v>
+        <v>40.42346172236243</v>
       </c>
       <c r="D5" t="n">
-        <v>30.53235360207581</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.59247689174634</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>44.71958967614647</v>
+        <v>31.75855648468008</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>30.51075515258238</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>23.1162314441954</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059792198347404</v>
+        <v>7.069631502815603</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18555185950692</v>
+        <v>67.16149927674822</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294844148760554</v>
+        <v>5.302223627111702</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.391357481095983</v>
+        <v>5.87281476680442</v>
       </c>
       <c r="C2" t="n">
-        <v>7.367034772668064</v>
+        <v>7.088218424661971</v>
       </c>
       <c r="D2" t="n">
-        <v>31.3334597287412</v>
+        <v>23.64932044760141</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.06063167795183</v>
+        <v>19.27170743436489</v>
       </c>
       <c r="C3" t="n">
-        <v>32.3633130704961</v>
+        <v>30.78760800517997</v>
       </c>
       <c r="D3" t="n">
-        <v>68.42781498600269</v>
+        <v>64.93279315888404</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.32047602440774</v>
+        <v>29.83923972287755</v>
       </c>
       <c r="C4" t="n">
-        <v>52.45477983790708</v>
+        <v>46.49458952542469</v>
       </c>
       <c r="D4" t="n">
-        <v>61.56736202872597</v>
+        <v>57.39395253797278</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.14532402242431</v>
+        <v>28.96155727528091</v>
       </c>
       <c r="C5" t="n">
-        <v>63.88723185386119</v>
+        <v>52.7443954106599</v>
       </c>
       <c r="D5" t="n">
-        <v>41.23340357836604</v>
+        <v>36.76645152404306</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.68935111929729</v>
+        <v>20.81010608691964</v>
       </c>
       <c r="C6" t="n">
-        <v>67.62278186852032</v>
+        <v>51.56237117474674</v>
       </c>
       <c r="D6" t="n">
-        <v>33.77113927838603</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -6140,10 +6140,10 @@
         <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>47.72962813736718</v>
+        <v>34.85400699617026</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>26.03594911662541</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.282426925039412</v>
+        <v>7.296918224604565</v>
       </c>
       <c r="C21" t="n">
-        <v>75.55517934728391</v>
+        <v>77.52975613642352</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372123559409486</v>
+        <v>6.384803446528995</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.130212591766331</v>
+        <v>5.185591373831652</v>
       </c>
       <c r="C2" t="n">
-        <v>5.974916528046087</v>
+        <v>4.300054944601029</v>
       </c>
       <c r="D2" t="n">
-        <v>27.1158715912969</v>
+        <v>27.50071669136165</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.88606051304514</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="C3" t="n">
-        <v>30.12001956629214</v>
+        <v>28.83393007372882</v>
       </c>
       <c r="D3" t="n">
-        <v>77.61697349775284</v>
+        <v>68.78615289805276</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.23412328416303</v>
+        <v>34.30619177720055</v>
       </c>
       <c r="C4" t="n">
-        <v>69.30157044278235</v>
+        <v>64.84738110861457</v>
       </c>
       <c r="D4" t="n">
-        <v>82.02600243752526</v>
+        <v>76.48698189016474</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.80924751240241</v>
+        <v>38.11635461738242</v>
       </c>
       <c r="C5" t="n">
-        <v>82.78587516061229</v>
+        <v>71.54486394698633</v>
       </c>
       <c r="D5" t="n">
-        <v>53.6525120370882</v>
+        <v>49.7746086053133</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.42396044398116</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="C6" t="n">
-        <v>85.77627866774809</v>
+        <v>70.03788122096746</v>
       </c>
       <c r="D6" t="n">
-        <v>39.44662275663685</v>
+        <v>37.59504658642736</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>75.63678837828701</v>
+        <v>57.3713723407751</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>46.64774216728719</v>
+        <v>35.88287859022092</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.84374755077128</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.492347942365194</v>
+        <v>7.512541671817922</v>
       </c>
       <c r="C21" t="n">
-        <v>85.22545784440408</v>
+        <v>87.33329693488334</v>
       </c>
       <c r="D21" t="n">
-        <v>7.492347942365194</v>
+        <v>7.512541671817922</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_93_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497637761287</v>
+        <v>10.84497648042691</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907210009712</v>
+        <v>37.78907245835031</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.585162689460105</v>
+        <v>6.836891012374788</v>
       </c>
       <c r="C2" t="n">
-        <v>5.929756133650734</v>
+        <v>13.07000718663779</v>
       </c>
       <c r="D2" t="n">
-        <v>36.37964292856981</v>
+        <v>28.58554790455438</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.75628988963531</v>
+        <v>19.38951715887451</v>
       </c>
       <c r="C3" t="n">
-        <v>21.80952524984289</v>
+        <v>26.32556468937822</v>
       </c>
       <c r="D3" t="n">
-        <v>74.38702355078082</v>
+        <v>56.15105994439632</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.84597308808704</v>
+        <v>33.66805576944012</v>
       </c>
       <c r="C4" t="n">
-        <v>68.9314515582813</v>
+        <v>51.61244030766331</v>
       </c>
       <c r="D4" t="n">
-        <v>92.82326368883167</v>
+        <v>84.24671574453154</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.01313223971626</v>
+        <v>45.03767593232243</v>
       </c>
       <c r="C5" t="n">
-        <v>96.92304210176638</v>
+        <v>62.66004722355269</v>
       </c>
       <c r="D5" t="n">
-        <v>64.59899893944014</v>
+        <v>69.80226177194822</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.02272873258048</v>
+        <v>45.88688769649593</v>
       </c>
       <c r="C6" t="n">
-        <v>93.30333831620838</v>
+        <v>82.51589454194442</v>
       </c>
       <c r="D6" t="n">
-        <v>44.67933802027235</v>
+        <v>47.65796055495717</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.90716024091983</v>
+        <v>33.83593462686632</v>
       </c>
       <c r="C7" t="n">
-        <v>80.72715022480672</v>
+        <v>91.20730696764143</v>
       </c>
       <c r="D7" t="n">
-        <v>38.92629647338602</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>17.60764507566654</v>
       </c>
       <c r="C8" t="n">
-        <v>56.66156875060466</v>
+        <v>70.93127163183205</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>36.27655941962388</v>
+        <v>42.59999638267758</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
         <v>35.16129402759952</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
         <v>34.49763257952867</v>
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.714561711917029</v>
+        <v>7.705332351133181</v>
       </c>
       <c r="C21" t="n">
-        <v>96.43202139896286</v>
+        <v>95.35348784527312</v>
       </c>
       <c r="D21" t="n">
-        <v>8.678881925906657</v>
+        <v>8.668498895024829</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.647413705455153</v>
+        <v>6.992007149645783</v>
       </c>
       <c r="C2" t="n">
-        <v>7.691011515069513</v>
+        <v>6.895795874629596</v>
       </c>
       <c r="D2" t="n">
-        <v>30.26728172192916</v>
+        <v>25.48322515913446</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.71211124294421</v>
+        <v>21.17138924208247</v>
       </c>
       <c r="C3" t="n">
-        <v>22.35439522569988</v>
+        <v>39.31408681656352</v>
       </c>
       <c r="D3" t="n">
-        <v>84.00815105239957</v>
+        <v>64.78062226472578</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.38651516249953</v>
+        <v>35.09748042682347</v>
       </c>
       <c r="C4" t="n">
-        <v>60.83988697987908</v>
+        <v>58.93824167675302</v>
       </c>
       <c r="D4" t="n">
-        <v>105.5221702432642</v>
+        <v>92.35104304308896</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.70097752749479</v>
+        <v>47.71293842639499</v>
       </c>
       <c r="C5" t="n">
-        <v>111.9928693619549</v>
+        <v>78.3189231062893</v>
       </c>
       <c r="D5" t="n">
-        <v>81.2150788338174</v>
+        <v>82.04956438242719</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.95859633663495</v>
+        <v>53.81646390369741</v>
       </c>
       <c r="C6" t="n">
-        <v>121.6807557074624</v>
+        <v>91.17000055488006</v>
       </c>
       <c r="D6" t="n">
-        <v>53.05168244208915</v>
+        <v>57.88188114698346</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.74663664350886</v>
+        <v>43.95677170994669</v>
       </c>
       <c r="C7" t="n">
-        <v>107.4365782665454</v>
+        <v>104.801567428347</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81892612072463</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.86352137357647</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="C8" t="n">
-        <v>80.69475255056658</v>
+        <v>96.21618375470864</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>64.45468202691582</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>36.58482819875739</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>28.61794557879453</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.901210177974066</v>
+        <v>7.894751404178972</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6786861304031</v>
+        <v>104.6054561053714</v>
       </c>
       <c r="D21" t="n">
-        <v>9.876512722467583</v>
+        <v>9.868439255223716</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.801949005649402</v>
+        <v>7.855945129382977</v>
       </c>
       <c r="C2" t="n">
-        <v>7.865762606425444</v>
+        <v>7.114725612676635</v>
       </c>
       <c r="D2" t="n">
-        <v>34.53690248769854</v>
+        <v>25.008059270279</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.09146676741098</v>
+        <v>22.00587479069226</v>
       </c>
       <c r="C3" t="n">
-        <v>25.82978209873358</v>
+        <v>32.86400439966197</v>
       </c>
       <c r="D3" t="n">
-        <v>87.11047379781949</v>
+        <v>68.5456247105123</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.37826027023806</v>
+        <v>36.99912572994954</v>
       </c>
       <c r="C4" t="n">
-        <v>57.75130870231862</v>
+        <v>77.64838942428872</v>
       </c>
       <c r="D4" t="n">
-        <v>118.6422465628185</v>
+        <v>100.3405058602495</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.56629816556373</v>
+        <v>50.19185137961819</v>
       </c>
       <c r="C5" t="n">
-        <v>111.8701508989241</v>
+        <v>91.40071126537806</v>
       </c>
       <c r="D5" t="n">
-        <v>97.43845964649596</v>
+        <v>94.22323591508764</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.9623844587317</v>
+        <v>58.56615929684348</v>
       </c>
       <c r="C6" t="n">
-        <v>145.5499876408151</v>
+        <v>105.4995900460665</v>
       </c>
       <c r="D6" t="n">
-        <v>63.35610634586367</v>
+        <v>67.58253021264619</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.80758711663017</v>
+        <v>52.99964981376406</v>
       </c>
       <c r="C7" t="n">
-        <v>138.3979556153771</v>
+        <v>118.0365082292982</v>
       </c>
       <c r="D7" t="n">
-        <v>47.66974152740813</v>
+        <v>49.22679338634357</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.45872252425729</v>
+        <v>36.13322425480386</v>
       </c>
       <c r="C8" t="n">
-        <v>107.5651872158018</v>
+        <v>115.6596970373167</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.64218617176442</v>
+        <v>19.30312336090078</v>
       </c>
       <c r="C9" t="n">
-        <v>73.66249374504666</v>
+        <v>89.85936736971051</v>
       </c>
       <c r="D9" t="n">
-        <v>37.82968428774233</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>9.252972112526189</v>
       </c>
       <c r="C10" t="n">
-        <v>48.54251523648354</v>
+        <v>56.37195317785186</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13853390395258</v>
+        <v>39.626282586514</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
         <v>35.36549755008285</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
         <v>33.82120841130262</v>
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1604,7 +1604,7 @@
         <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.072902895865148</v>
+        <v>8.06953531900457</v>
       </c>
       <c r="C21" t="n">
-        <v>114.0297534040952</v>
+        <v>112.973494466064</v>
       </c>
       <c r="D21" t="n">
-        <v>11.10024148181458</v>
+        <v>11.09561106363128</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.072510461394022</v>
+        <v>7.157922511663494</v>
       </c>
       <c r="C2" t="n">
-        <v>5.285729639664827</v>
+        <v>4.724169952835651</v>
       </c>
       <c r="D2" t="n">
-        <v>28.02202472231671</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.60259746842507</v>
+        <v>26.55627539987622</v>
       </c>
       <c r="C3" t="n">
-        <v>38.57286729985718</v>
+        <v>47.85529184351077</v>
       </c>
       <c r="D3" t="n">
-        <v>95.23934478898308</v>
+        <v>75.65347808925921</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.77243982125977</v>
+        <v>24.10877837318892</v>
       </c>
       <c r="C4" t="n">
-        <v>88.54775243683682</v>
+        <v>90.34729597872122</v>
       </c>
       <c r="D4" t="n">
-        <v>113.1159887356133</v>
+        <v>99.85552249435158</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.64311116620645</v>
+        <v>32.98672286269284</v>
       </c>
       <c r="C5" t="n">
-        <v>86.95830290366123</v>
+        <v>63.02820261264524</v>
       </c>
       <c r="D5" t="n">
-        <v>64.96715432853269</v>
+        <v>66.6115817331461</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.30949687321178</v>
+        <v>32.88560284915541</v>
       </c>
       <c r="C6" t="n">
-        <v>91.12974889900595</v>
+        <v>77.72594749292425</v>
       </c>
       <c r="D6" t="n">
-        <v>31.396291581813</v>
+        <v>32.40258297866598</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>23.95464398362217</v>
       </c>
       <c r="C7" t="n">
-        <v>75.63678837828701</v>
+        <v>81.32601632439727</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>54.24156065963627</v>
+        <v>66.17470400475625</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>37.05312185368311</v>
+        <v>43.04374634499714</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
         <v>28.25371718051895</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>27.55471281509523</v>
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
         <v>24.89024954576939</v>
@@ -1901,7 +1901,7 @@
         <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.280419990516093</v>
+        <v>4.400193210434204</v>
       </c>
       <c r="C2" t="n">
-        <v>2.510328879759094</v>
+        <v>2.240348261091221</v>
       </c>
       <c r="D2" t="n">
-        <v>19.6074651492173</v>
+        <v>14.03015644139117</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.22109852210056</v>
+        <v>26.50227927614264</v>
       </c>
       <c r="C3" t="n">
-        <v>29.71750300755095</v>
+        <v>32.98181412417159</v>
       </c>
       <c r="D3" t="n">
-        <v>96.9721294869787</v>
+        <v>75.64366061221675</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.68907338185679</v>
+        <v>36.16954891986099</v>
       </c>
       <c r="C4" t="n">
-        <v>95.73316388421922</v>
+        <v>107.4238155463902</v>
       </c>
       <c r="D4" t="n">
-        <v>132.502560651375</v>
+        <v>112.6437680898705</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.47192721276901</v>
+        <v>36.57010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>124.5101525911018</v>
+        <v>112.5573742918968</v>
       </c>
       <c r="D5" t="n">
-        <v>83.27674901273571</v>
+        <v>83.35038009055421</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.14598697495907</v>
+        <v>39.36611944488861</v>
       </c>
       <c r="C6" t="n">
-        <v>114.0329410913798</v>
+        <v>91.77377539299185</v>
       </c>
       <c r="D6" t="n">
-        <v>39.1246095096439</v>
+        <v>40.33215918586747</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>22.69702517448201</v>
       </c>
       <c r="C7" t="n">
-        <v>99.2919993121139</v>
+        <v>97.37562779342413</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>70.68092596724911</v>
+        <v>84.5333860741716</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>43.59843379789659</v>
+        <v>50.25468323268996</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2156,7 +2156,7 @@
         <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
         <v>26.27647730416588</v>
@@ -2198,7 +2198,7 @@
         <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.072109550766522</v>
+        <v>4.482660017590937</v>
       </c>
       <c r="C2" t="n">
-        <v>8.153414683769761</v>
+        <v>8.019896995992195</v>
       </c>
       <c r="D2" t="n">
-        <v>16.91943993498953</v>
+        <v>22.03532722181966</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.777307502052</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="C3" t="n">
-        <v>18.72683745850791</v>
+        <v>19.71840263979719</v>
       </c>
       <c r="D3" t="n">
-        <v>90.45332473077987</v>
+        <v>69.64518213926873</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.74685762768712</v>
+        <v>43.72507925174444</v>
       </c>
       <c r="C4" t="n">
-        <v>85.254970636793</v>
+        <v>94.15058658497337</v>
       </c>
       <c r="D4" t="n">
-        <v>149.1451477337669</v>
+        <v>123.7345719047467</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.95775345765094</v>
+        <v>44.98858854711009</v>
       </c>
       <c r="C5" t="n">
-        <v>150.5019230610361</v>
+        <v>156.2451471308799</v>
       </c>
       <c r="D5" t="n">
-        <v>108.7285582453343</v>
+        <v>102.5435477085794</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.46549694719579</v>
+        <v>44.47807974090175</v>
       </c>
       <c r="C6" t="n">
-        <v>155.5323982975967</v>
+        <v>135.366318704663</v>
       </c>
       <c r="D6" t="n">
-        <v>53.53470231257858</v>
+        <v>54.58124536530568</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.22466566001905</v>
+        <v>33.0574086973986</v>
       </c>
       <c r="C7" t="n">
-        <v>130.2533766609455</v>
+        <v>115.9404768807313</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C8" t="n">
-        <v>99.80447161373074</v>
+        <v>106.814150222053</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>64.12186955517615</v>
+        <v>74.99374363200533</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>41.14013754646259</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.536255230697011</v>
+        <v>2.621266370338984</v>
       </c>
       <c r="C2" t="n">
-        <v>3.672718161587317</v>
+        <v>3.628539514896211</v>
       </c>
       <c r="D2" t="n">
-        <v>11.70537787773472</v>
+        <v>15.17291076913445</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.6082669704723</v>
+        <v>20.4841658491097</v>
       </c>
       <c r="C3" t="n">
-        <v>25.85432579133975</v>
+        <v>26.22738991895354</v>
       </c>
       <c r="D3" t="n">
-        <v>87.62589134254907</v>
+        <v>72.51188543566941</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.14999608123406</v>
+        <v>48.20479402622264</v>
       </c>
       <c r="C4" t="n">
-        <v>79.8435772909846</v>
+        <v>86.40361545076178</v>
       </c>
       <c r="D4" t="n">
-        <v>160.0189853060046</v>
+        <v>131.4049667180271</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.04396732917541</v>
+        <v>47.19752088166541</v>
       </c>
       <c r="C5" t="n">
-        <v>174.284761196415</v>
+        <v>184.4458499353695</v>
       </c>
       <c r="D5" t="n">
-        <v>118.5705789804085</v>
+        <v>110.8393158094649</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.783722072092</v>
+        <v>39.40637110076273</v>
       </c>
       <c r="C6" t="n">
-        <v>189.5047958553534</v>
+        <v>167.446888436336</v>
       </c>
       <c r="D6" t="n">
-        <v>52.68941753922207</v>
+        <v>53.69570893607505</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.982991493858314</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>135.104192067629</v>
+        <v>129.8341703912322</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>79.52647278251287</v>
+        <v>89.79064503041327</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39530983410874</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
         <v>32.50468473990763</v>
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.87201294554942</v>
+        <v>3.319288988058466</v>
       </c>
       <c r="C2" t="n">
-        <v>4.318708150981719</v>
+        <v>4.80467326458389</v>
       </c>
       <c r="D2" t="n">
-        <v>11.27340888786612</v>
+        <v>19.2049485904761</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98423528346982</v>
+        <v>14.8047553800419</v>
       </c>
       <c r="C3" t="n">
-        <v>19.90002596508285</v>
+        <v>19.88039101099791</v>
       </c>
       <c r="D3" t="n">
-        <v>77.77896186895356</v>
+        <v>68.69779560467056</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.91652005407257</v>
+        <v>44.47807974090174</v>
       </c>
       <c r="C4" t="n">
-        <v>72.12213159708342</v>
+        <v>75.68293052038661</v>
       </c>
       <c r="D4" t="n">
-        <v>166.2089045812808</v>
+        <v>136.727021022749</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.47503668679778</v>
+        <v>58.4385320952914</v>
       </c>
       <c r="C5" t="n">
-        <v>162.7737693641212</v>
+        <v>173.7693436516855</v>
       </c>
       <c r="D5" t="n">
-        <v>143.9978445204009</v>
+        <v>129.2470852640926</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.81267578160067</v>
+        <v>49.79129831628549</v>
       </c>
       <c r="C6" t="n">
-        <v>231.1652596850668</v>
+        <v>228.7501603326196</v>
       </c>
       <c r="D6" t="n">
-        <v>72.89574878802993</v>
+        <v>71.92970904705108</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>22.87668500435917</v>
       </c>
       <c r="C7" t="n">
-        <v>198.1049057445554</v>
+        <v>180.1389227568388</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>121.5010958775852</v>
+        <v>127.1755976081318</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>63.45624461169682</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
         <v>21.91359050649305</v>
@@ -3117,7 +3117,7 @@
         <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>35.41654843070368</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.704714925199963</v>
+        <v>2.530945581548277</v>
       </c>
       <c r="C2" t="n">
-        <v>2.649737053762141</v>
+        <v>2.692933952749001</v>
       </c>
       <c r="D2" t="n">
-        <v>8.718901361415924</v>
+        <v>13.99874051485527</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.55579237379071</v>
+        <v>13.48921345635117</v>
       </c>
       <c r="C3" t="n">
-        <v>18.83482970597506</v>
+        <v>19.71840263979719</v>
       </c>
       <c r="D3" t="n">
-        <v>70.97545027852316</v>
+        <v>69.0070461315083</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.08770400751001</v>
+        <v>39.28365263773187</v>
       </c>
       <c r="C4" t="n">
-        <v>63.58387181324892</v>
+        <v>66.14917856444583</v>
       </c>
       <c r="D4" t="n">
-        <v>167.5872783580433</v>
+        <v>139.5092940165845</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.14462967882311</v>
+        <v>63.91177554646737</v>
       </c>
       <c r="C5" t="n">
-        <v>156.6133025199724</v>
+        <v>164.5900026169778</v>
       </c>
       <c r="D5" t="n">
-        <v>162.601963515878</v>
+        <v>143.1879026643973</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.6680400739069</v>
+        <v>58.44540432922113</v>
       </c>
       <c r="C6" t="n">
-        <v>252.176624051357</v>
+        <v>258.8986505823349</v>
       </c>
       <c r="D6" t="n">
-        <v>87.54735152620934</v>
+        <v>84.56872899152451</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>22.15804568485051</v>
       </c>
       <c r="C7" t="n">
-        <v>248.7689777699162</v>
+        <v>231.4617474917492</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>45.87314322863646</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>159.5536368941916</v>
+        <v>162.8081305337698</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>68.11561921605218</v>
+        <v>75.32655610374501</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3414,7 +3414,7 @@
         <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.41982816451914</v>
+        <v>4.799764526062656</v>
       </c>
       <c r="C2" t="n">
-        <v>6.592435834017332</v>
+        <v>4.637776154861932</v>
       </c>
       <c r="D2" t="n">
-        <v>18.86330038939822</v>
+        <v>15.10124318672444</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.45837836689202</v>
+        <v>11.08393158094649</v>
       </c>
       <c r="C3" t="n">
-        <v>14.8194815956056</v>
+        <v>15.17291076913446</v>
       </c>
       <c r="D3" t="n">
-        <v>63.49453277216247</v>
+        <v>65.26658737832796</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.94432778496097</v>
+        <v>32.80019079888594</v>
       </c>
       <c r="C4" t="n">
-        <v>55.93900244027901</v>
+        <v>58.19800390775092</v>
       </c>
       <c r="D4" t="n">
-        <v>163.3117671060484</v>
+        <v>139.6752093786022</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.02191121579226</v>
+        <v>62.68459091615885</v>
       </c>
       <c r="C5" t="n">
-        <v>139.1627370769854</v>
+        <v>145.3722913063465</v>
       </c>
       <c r="D5" t="n">
-        <v>180.6415775814131</v>
+        <v>156.834195753428</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.61649047166733</v>
+        <v>68.79007988886977</v>
       </c>
       <c r="C6" t="n">
-        <v>251.8143591484899</v>
+        <v>261.0319883436633</v>
       </c>
       <c r="D6" t="n">
-        <v>110.4505437185832</v>
+        <v>103.648013875857</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.2133266559246</v>
+        <v>39.22572952318131</v>
       </c>
       <c r="C7" t="n">
-        <v>296.9776987869558</v>
+        <v>293.863595069085</v>
       </c>
       <c r="D7" t="n">
-        <v>55.81432048183967</v>
+        <v>55.57477404200344</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C8" t="n">
-        <v>228.8159374288041</v>
+        <v>220.6379790524282</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>116.7062400900438</v>
+        <v>124.3609269400562</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>54.09429850399926</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.504258467084366</v>
+        <v>6.748533718992575</v>
       </c>
       <c r="C2" t="n">
-        <v>4.430627389265855</v>
+        <v>7.192283681312134</v>
       </c>
       <c r="D2" t="n">
-        <v>8.933904108645974</v>
+        <v>9.433613690107601</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.126866438026091</v>
+        <v>3.39488356128547</v>
       </c>
       <c r="C2" t="n">
-        <v>3.691371367968007</v>
+        <v>2.59770442543706</v>
       </c>
       <c r="D2" t="n">
-        <v>13.88387603345839</v>
+        <v>11.11534750748239</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.96950906790612</v>
+        <v>15.61469723604552</v>
       </c>
       <c r="C3" t="n">
-        <v>20.43016972537612</v>
+        <v>18.38322576202152</v>
       </c>
       <c r="D3" t="n">
-        <v>71.21106972754238</v>
+        <v>70.57784245830321</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.36245449597887</v>
+        <v>46.78813208899449</v>
       </c>
       <c r="C4" t="n">
-        <v>79.66489920881168</v>
+        <v>82.90663012823464</v>
       </c>
       <c r="D4" t="n">
-        <v>167.446888436336</v>
+        <v>144.8313483213065</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.80986940720817</v>
+        <v>41.06159773012285</v>
       </c>
       <c r="C5" t="n">
-        <v>211.0512127204581</v>
+        <v>217.947990342792</v>
       </c>
       <c r="D5" t="n">
-        <v>164.7863521578271</v>
+        <v>145.3722913063465</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.85664913964674</v>
+        <v>24.35225180384214</v>
       </c>
       <c r="C6" t="n">
-        <v>247.4269286582109</v>
+        <v>249.8420280106581</v>
       </c>
       <c r="D6" t="n">
-        <v>86.09829191474104</v>
+        <v>82.2341329508256</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>7.60559946480004</v>
       </c>
       <c r="C7" t="n">
-        <v>160.915320959982</v>
+        <v>155.1662064039126</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>85.95201150680825</v>
+        <v>91.6265132373548</v>
       </c>
       <c r="D8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>41.26874649571891</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.91890015564179</v>
+        <v>23.48831382410494</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.404922022506191</v>
+        <v>6.857507714163971</v>
       </c>
       <c r="C2" t="n">
-        <v>5.087416603406972</v>
+        <v>4.977460860531329</v>
       </c>
       <c r="D2" t="n">
-        <v>8.727737090754145</v>
+        <v>12.01462840457247</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.572040116406402</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C3" t="n">
-        <v>11.33918598405066</v>
+        <v>18.12306262039612</v>
       </c>
       <c r="D3" t="n">
-        <v>10.64214511403542</v>
+        <v>11.05938788834032</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39893532535591</v>
+        <v>13.39798914775357</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14736729156917</v>
+        <v>70.14241377353342</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576345332394813</v>
+        <v>1.576234017382773</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.314781160164732</v>
+        <v>5.751078051477815</v>
       </c>
       <c r="C2" t="n">
-        <v>3.531346492175777</v>
+        <v>4.231332605303753</v>
       </c>
       <c r="D2" t="n">
-        <v>17.93358531347648</v>
+        <v>27.32694734770996</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.31802950291373</v>
+        <v>19.96874830438012</v>
       </c>
       <c r="C3" t="n">
-        <v>16.74861583445059</v>
+        <v>18.9280957378785</v>
       </c>
       <c r="D3" t="n">
-        <v>15.39871274111122</v>
+        <v>18.47649179392497</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.23119373658351</v>
+        <v>16.61706164208151</v>
       </c>
       <c r="C4" t="n">
-        <v>18.0975371800857</v>
+        <v>28.15456066239003</v>
       </c>
       <c r="D4" t="n">
-        <v>20.65008121112741</v>
+        <v>20.86704745376596</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.092505268377454</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44543456152856</v>
+        <v>15.44141430078881</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16926650115936</v>
+        <v>86.14683767808492</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251670434006014</v>
+        <v>3.25082406332396</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.634250074672444</v>
+        <v>5.205226327916588</v>
       </c>
       <c r="C2" t="n">
-        <v>4.482660017590937</v>
+        <v>2.530945581548277</v>
       </c>
       <c r="D2" t="n">
-        <v>27.07463818771854</v>
+        <v>27.04224051347839</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.00248757922301</v>
+        <v>19.94420461177396</v>
       </c>
       <c r="C3" t="n">
-        <v>15.06491852166731</v>
+        <v>17.43583922742335</v>
       </c>
       <c r="D3" t="n">
-        <v>26.16848505669873</v>
+        <v>36.04977569994288</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.14706653365455</v>
+        <v>29.17557827480671</v>
       </c>
       <c r="C4" t="n">
-        <v>31.95785126864217</v>
+        <v>39.48785616021521</v>
       </c>
       <c r="D4" t="n">
-        <v>23.53445596620454</v>
+        <v>25.44886398948582</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.35743827980385</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C5" t="n">
-        <v>21.64753687864217</v>
+        <v>31.95588777323368</v>
       </c>
       <c r="D5" t="n">
-        <v>30.23782929080177</v>
+        <v>29.94330497952772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.997496725243765</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74500217290594</v>
+        <v>16.73395580921335</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1445132547262</v>
+        <v>102.0771304362014</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023500651871783</v>
+        <v>5.020186742764006</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.858088551240718</v>
+        <v>5.049128442941345</v>
       </c>
       <c r="C2" t="n">
-        <v>7.099017649408686</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="D2" t="n">
-        <v>31.34229545807942</v>
+        <v>21.34712208114264</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81381209355838</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="C3" t="n">
-        <v>16.4344565690916</v>
+        <v>13.03270077387641</v>
       </c>
       <c r="D3" t="n">
-        <v>40.92415305152829</v>
+        <v>48.58178514465342</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.75891633757857</v>
+        <v>34.43381897875263</v>
       </c>
       <c r="C4" t="n">
-        <v>35.23787034853076</v>
+        <v>41.79790850830795</v>
       </c>
       <c r="D4" t="n">
-        <v>30.70710469343173</v>
+        <v>37.12675293150163</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.53740120931728</v>
+        <v>28.91246989006857</v>
       </c>
       <c r="C5" t="n">
-        <v>42.21515128261285</v>
+        <v>53.77523050011905</v>
       </c>
       <c r="D5" t="n">
-        <v>32.05406254365837</v>
+        <v>32.00497515844602</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.982410656781569</v>
+        <v>12.7597749120958</v>
       </c>
       <c r="C6" t="n">
-        <v>23.78872862160447</v>
+        <v>32.52333794628834</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07922455409803</v>
+        <v>18.05938714664659</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9454173291157</v>
+        <v>117.8160018614563</v>
       </c>
       <c r="D21" t="n">
-        <v>6.887323639656394</v>
+        <v>6.879766532055842</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.821763886183585</v>
+        <v>5.521349088684061</v>
       </c>
       <c r="C2" t="n">
-        <v>9.053677328564085</v>
+        <v>4.963716392671873</v>
       </c>
       <c r="D2" t="n">
-        <v>29.25411809114646</v>
+        <v>19.48867367700343</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.09222753093697</v>
+        <v>15.96812640957437</v>
       </c>
       <c r="C3" t="n">
-        <v>21.57881453934489</v>
+        <v>12.07058802371454</v>
       </c>
       <c r="D3" t="n">
-        <v>52.34187885191869</v>
+        <v>50.80544369477244</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.97289627937536</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C4" t="n">
-        <v>32.34073287329843</v>
+        <v>30.33698580893068</v>
       </c>
       <c r="D4" t="n">
-        <v>37.79041437957247</v>
+        <v>45.32041927114551</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.32217747790898</v>
+        <v>24.74004214701963</v>
       </c>
       <c r="C5" t="n">
-        <v>40.42346172236243</v>
+        <v>49.5291716792516</v>
       </c>
       <c r="D5" t="n">
-        <v>29.18245050873644</v>
+        <v>30.97414006898687</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.5119735799981</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>31.75855648468008</v>
+        <v>40.57366912111219</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>31.07427833482005</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>17.96598298771663</v>
+        <v>22.21793229480956</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.069631502815603</v>
+        <v>7.059385680006153</v>
       </c>
       <c r="C21" t="n">
-        <v>67.16149927674822</v>
+        <v>66.18174075005768</v>
       </c>
       <c r="D21" t="n">
-        <v>5.302223627111702</v>
+        <v>5.294539260004615</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.87281476680442</v>
+        <v>4.873395603881167</v>
       </c>
       <c r="C2" t="n">
-        <v>7.088218424661971</v>
+        <v>7.895215037552849</v>
       </c>
       <c r="D2" t="n">
-        <v>23.64932044760141</v>
+        <v>14.66829244915159</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.27170743436489</v>
+        <v>18.18196748265093</v>
       </c>
       <c r="C3" t="n">
-        <v>30.78760800517997</v>
+        <v>16.87624303600267</v>
       </c>
       <c r="D3" t="n">
-        <v>64.93279315888404</v>
+        <v>55.18894719423445</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.83923972287755</v>
+        <v>29.5967480399286</v>
       </c>
       <c r="C4" t="n">
-        <v>46.49458952542469</v>
+        <v>30.33698580893068</v>
       </c>
       <c r="D4" t="n">
-        <v>57.39395253797278</v>
+        <v>62.25654891710723</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.96155727528091</v>
+        <v>33.30579086657305</v>
       </c>
       <c r="C5" t="n">
-        <v>52.7443954106599</v>
+        <v>53.72614311490671</v>
       </c>
       <c r="D5" t="n">
-        <v>36.76645152404306</v>
+        <v>41.35612204139689</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.81010608691964</v>
+        <v>25.47929816831747</v>
       </c>
       <c r="C6" t="n">
-        <v>51.56237117474674</v>
+        <v>63.07434475474484</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52962934314132</v>
+        <v>34.09315252537899</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>12.57618809140164</v>
       </c>
       <c r="C7" t="n">
-        <v>34.85400699617026</v>
+        <v>44.25620475974196</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>22.19731559302038</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6241,7 +6241,7 @@
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.296918224604565</v>
+        <v>7.285423968959598</v>
       </c>
       <c r="C21" t="n">
-        <v>77.52975613642352</v>
+        <v>76.49695167407577</v>
       </c>
       <c r="D21" t="n">
-        <v>6.384803446528995</v>
+        <v>6.374745972839648</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.185591373831652</v>
+        <v>6.114324702049134</v>
       </c>
       <c r="C2" t="n">
-        <v>4.300054944601029</v>
+        <v>6.957645979997145</v>
       </c>
       <c r="D2" t="n">
-        <v>27.50071669136165</v>
+        <v>18.5147799543906</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.95402208881642</v>
+        <v>17.48983535115693</v>
       </c>
       <c r="C3" t="n">
-        <v>28.83393007372882</v>
+        <v>25.42726553999239</v>
       </c>
       <c r="D3" t="n">
-        <v>68.78615289805276</v>
+        <v>54.11884219660542</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.30619177720055</v>
+        <v>32.99163160121406</v>
       </c>
       <c r="C4" t="n">
-        <v>64.84738110861457</v>
+        <v>37.20332925243288</v>
       </c>
       <c r="D4" t="n">
-        <v>76.48698189016474</v>
+        <v>75.35109979635119</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.11635461738242</v>
+        <v>40.05530633326987</v>
       </c>
       <c r="C5" t="n">
-        <v>71.54486394698633</v>
+        <v>55.19876467127693</v>
       </c>
       <c r="D5" t="n">
-        <v>49.7746086053133</v>
+        <v>55.12513359345841</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.99377502307181</v>
+        <v>36.4277485660779</v>
       </c>
       <c r="C6" t="n">
-        <v>70.03788122096746</v>
+        <v>75.99512629033711</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>39.40637110076273</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>57.3713723407751</v>
+        <v>70.90574619152163</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>35.88287859022092</v>
+        <v>44.2277340763188</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.18124777685393</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.512541671817922</v>
+        <v>7.501406726630605</v>
       </c>
       <c r="C21" t="n">
-        <v>87.33329693488334</v>
+        <v>86.26617735625194</v>
       </c>
       <c r="D21" t="n">
-        <v>7.512541671817922</v>
+        <v>7.501406726630605</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_93_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497648042691</v>
+        <v>10.84497647129616</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907245835031</v>
+        <v>37.78907242653441</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.836891012374788</v>
+        <v>1.578650308428871</v>
       </c>
       <c r="C2" t="n">
-        <v>13.07000718663779</v>
+        <v>3.545090960035232</v>
       </c>
       <c r="D2" t="n">
-        <v>28.58554790455438</v>
+        <v>12.83929647613979</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.38951715887451</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C3" t="n">
-        <v>26.32556468937822</v>
+        <v>42.64221153396021</v>
       </c>
       <c r="D3" t="n">
-        <v>56.15105994439632</v>
+        <v>58.24709129296326</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.66805576944012</v>
+        <v>17.71465557542945</v>
       </c>
       <c r="C4" t="n">
-        <v>51.61244030766331</v>
+        <v>118.9996027271644</v>
       </c>
       <c r="D4" t="n">
-        <v>84.24671574453154</v>
+        <v>72.3518605598772</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.03767593232243</v>
+        <v>17.13149743910684</v>
       </c>
       <c r="C5" t="n">
-        <v>62.66004722355269</v>
+        <v>128.8789298750001</v>
       </c>
       <c r="D5" t="n">
-        <v>69.80226177194822</v>
+        <v>48.35107443415542</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.88688769649593</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>82.51589454194442</v>
+        <v>84.16621243278331</v>
       </c>
       <c r="D6" t="n">
-        <v>47.65796055495717</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.83593462686632</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>91.20730696764143</v>
+        <v>41.20198765183014</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.60764507566654</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>70.93127163183205</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>42.59999638267758</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.705332351133181</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.35348784527312</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.668498895024829</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.992007149645783</v>
+        <v>0.920879346583508</v>
       </c>
       <c r="C2" t="n">
-        <v>6.895795874629596</v>
+        <v>6.699446333780234</v>
       </c>
       <c r="D2" t="n">
-        <v>25.48322515913446</v>
+        <v>21.77909107101124</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.17138924208247</v>
+        <v>8.241771977151974</v>
       </c>
       <c r="C3" t="n">
-        <v>39.31408681656352</v>
+        <v>26.09485397888022</v>
       </c>
       <c r="D3" t="n">
-        <v>64.78062226472578</v>
+        <v>55.04659377711866</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.09748042682347</v>
+        <v>20.27996232662636</v>
       </c>
       <c r="C4" t="n">
-        <v>58.93824167675302</v>
+        <v>112.1460220038174</v>
       </c>
       <c r="D4" t="n">
-        <v>92.35104304308896</v>
+        <v>84.56578374841175</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.71293842639499</v>
+        <v>21.96660488252239</v>
       </c>
       <c r="C5" t="n">
-        <v>78.3189231062893</v>
+        <v>179.2425871028614</v>
       </c>
       <c r="D5" t="n">
-        <v>82.04956438242719</v>
+        <v>62.561872453128</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C6" t="n">
-        <v>91.17000055488006</v>
+        <v>146.3550207582975</v>
       </c>
       <c r="D6" t="n">
-        <v>57.88188114698346</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.95677170994669</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>104.801567428347</v>
+        <v>81.08646988456105</v>
       </c>
       <c r="D7" t="n">
-        <v>43.41779222031519</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>96.21618375470864</v>
+        <v>41.47393176590651</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>64.45468202691582</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
         <v>35.38905949498476</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.07910495788326</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.894751404178972</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6054561053714</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.868439255223716</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.855945129382977</v>
+        <v>0.4967643383488861</v>
       </c>
       <c r="C2" t="n">
-        <v>7.114725612676635</v>
+        <v>2.818597658892593</v>
       </c>
       <c r="D2" t="n">
-        <v>25.008059270279</v>
+        <v>14.84402528821177</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.00587479069226</v>
+        <v>6.970408700152354</v>
       </c>
       <c r="C3" t="n">
-        <v>32.86400439966197</v>
+        <v>27.89145227765188</v>
       </c>
       <c r="D3" t="n">
-        <v>68.5456247105123</v>
+        <v>60.09768571546849</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.99912572994954</v>
+        <v>22.24542123052848</v>
       </c>
       <c r="C4" t="n">
-        <v>77.64838942428872</v>
+        <v>104.6415425525548</v>
       </c>
       <c r="D4" t="n">
-        <v>100.3405058602495</v>
+        <v>92.23617856169209</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.19185137961819</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="C5" t="n">
-        <v>91.40071126537806</v>
+        <v>211.6402613430062</v>
       </c>
       <c r="D5" t="n">
-        <v>94.22323591508764</v>
+        <v>69.90043654237292</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.56615929684348</v>
+        <v>13.52455637370406</v>
       </c>
       <c r="C6" t="n">
-        <v>105.4995900460665</v>
+        <v>185.1576170209485</v>
       </c>
       <c r="D6" t="n">
-        <v>67.58253021264619</v>
+        <v>38.56108632740622</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.99964981376406</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>118.0365082292982</v>
+        <v>76.11588125795946</v>
       </c>
       <c r="D7" t="n">
-        <v>49.22679338634357</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.13322425480386</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>115.6596970373167</v>
+        <v>39.80496066868692</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.30312336090078</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>89.85936736971051</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>56.37195317785186</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.626282586514</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.06953531900457</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.973494466064</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09561106363128</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.157922511663494</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C2" t="n">
-        <v>4.724169952835651</v>
+        <v>3.714933312869931</v>
       </c>
       <c r="D2" t="n">
-        <v>20.33199495495144</v>
+        <v>12.42990768346887</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.55627539987622</v>
+        <v>4.275511251994859</v>
       </c>
       <c r="C3" t="n">
-        <v>47.85529184351077</v>
+        <v>18.51576170209485</v>
       </c>
       <c r="D3" t="n">
-        <v>75.65347808925921</v>
+        <v>57.99183688985909</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.10877837318892</v>
+        <v>18.19963894132737</v>
       </c>
       <c r="C4" t="n">
-        <v>90.34729597872122</v>
+        <v>86.81202249572846</v>
       </c>
       <c r="D4" t="n">
-        <v>99.85552249435158</v>
+        <v>100.493658502112</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.98672286269284</v>
+        <v>27.46439202630453</v>
       </c>
       <c r="C5" t="n">
-        <v>63.02820261264524</v>
+        <v>204.1544350981243</v>
       </c>
       <c r="D5" t="n">
-        <v>66.6115817331461</v>
+        <v>85.31387549904784</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.88560284915541</v>
+        <v>20.44784118405257</v>
       </c>
       <c r="C6" t="n">
-        <v>77.72594749292425</v>
+        <v>261.5150082141527</v>
       </c>
       <c r="D6" t="n">
-        <v>32.40258297866598</v>
+        <v>50.07305990740432</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.95464398362217</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>81.32601632439727</v>
+        <v>163.4904451882213</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>66.17470400475625</v>
+        <v>66.50849822420017</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>43.04374634499714</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.400193210434204</v>
+        <v>0.3475386873033709</v>
       </c>
       <c r="C2" t="n">
-        <v>2.240348261091221</v>
+        <v>2.629120351972958</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03015644139117</v>
+        <v>8.939794594871456</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.50227927614264</v>
+        <v>3.215223731408304</v>
       </c>
       <c r="C3" t="n">
-        <v>32.98181412417159</v>
+        <v>16.84679060487527</v>
       </c>
       <c r="D3" t="n">
-        <v>75.64366061221675</v>
+        <v>55.77308707826131</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.16954891986099</v>
+        <v>14.68989089864502</v>
       </c>
       <c r="C4" t="n">
-        <v>107.4238155463902</v>
+        <v>70.05457093193965</v>
       </c>
       <c r="D4" t="n">
-        <v>112.6437680898705</v>
+        <v>105.637034724661</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.57010198319369</v>
+        <v>29.05973204570559</v>
       </c>
       <c r="C5" t="n">
-        <v>112.5573742918968</v>
+        <v>192.7416180362551</v>
       </c>
       <c r="D5" t="n">
-        <v>83.35038009055421</v>
+        <v>97.80661503558851</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.36611944488861</v>
+        <v>25.03652995370216</v>
       </c>
       <c r="C6" t="n">
-        <v>91.77377539299185</v>
+        <v>297.6609951891118</v>
       </c>
       <c r="D6" t="n">
-        <v>40.33215918586747</v>
+        <v>59.04917916733292</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.69702517448201</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C7" t="n">
-        <v>97.37562779342413</v>
+        <v>238.7080272967949</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>40.54323494228053</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>84.5333860741716</v>
+        <v>104.8113849053895</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>50.25468323268996</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.482660017590937</v>
+        <v>0.9336420667387166</v>
       </c>
       <c r="C2" t="n">
-        <v>8.019896995992195</v>
+        <v>11.94688781297944</v>
       </c>
       <c r="D2" t="n">
-        <v>22.03532722181966</v>
+        <v>12.63509295365645</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.61179305066178</v>
+        <v>2.208932334555323</v>
       </c>
       <c r="C3" t="n">
-        <v>19.71840263979719</v>
+        <v>13.40085616296896</v>
       </c>
       <c r="D3" t="n">
-        <v>69.64518213926873</v>
+        <v>51.05088062083414</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.72507925174444</v>
+        <v>10.73344765053038</v>
       </c>
       <c r="C4" t="n">
-        <v>94.15058658497337</v>
+        <v>56.24530772400401</v>
       </c>
       <c r="D4" t="n">
-        <v>123.7345719047467</v>
+        <v>107.4493409867007</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.98858854711009</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="C5" t="n">
-        <v>156.2451471308799</v>
+        <v>164.3936530761284</v>
       </c>
       <c r="D5" t="n">
-        <v>102.5435477085794</v>
+        <v>111.0111216577081</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.47807974090175</v>
+        <v>31.11452999069417</v>
       </c>
       <c r="C6" t="n">
-        <v>135.366318704663</v>
+        <v>302.6924521733766</v>
       </c>
       <c r="D6" t="n">
-        <v>54.58124536530568</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.0574086973986</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>115.9404768807313</v>
+        <v>324.9447456378347</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>46.59178254814513</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.35591675275186</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>106.814150222053</v>
+        <v>191.7647790705294</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>74.99374363200533</v>
+        <v>80.54061816099981</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.621266370338984</v>
+        <v>0.6342090169434395</v>
       </c>
       <c r="C2" t="n">
-        <v>3.628539514896211</v>
+        <v>6.403940274801944</v>
       </c>
       <c r="D2" t="n">
-        <v>15.17291076913445</v>
+        <v>9.197994241088367</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.4841658491097</v>
+        <v>3.637375244234433</v>
       </c>
       <c r="C3" t="n">
-        <v>26.22738991895354</v>
+        <v>26.70353755551324</v>
       </c>
       <c r="D3" t="n">
-        <v>72.51188543566941</v>
+        <v>55.93507544946203</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.20479402622264</v>
+        <v>17.91885909791278</v>
       </c>
       <c r="C4" t="n">
-        <v>86.40361545076178</v>
+        <v>81.98771427705964</v>
       </c>
       <c r="D4" t="n">
-        <v>131.4049667180271</v>
+        <v>109.6955797340174</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.19752088166541</v>
+        <v>18.97227438456961</v>
       </c>
       <c r="C5" t="n">
-        <v>184.4458499353695</v>
+        <v>251.0819753611218</v>
       </c>
       <c r="D5" t="n">
-        <v>110.8393158094649</v>
+        <v>103.3780332571892</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.40637110076273</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>167.446888436336</v>
+        <v>285.2232335240089</v>
       </c>
       <c r="D6" t="n">
-        <v>53.69570893607505</v>
+        <v>62.792583163626</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>129.8341703912322</v>
+        <v>134.8646456277928</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>89.79064503041327</v>
+        <v>59.33192250615598</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.40043955680824</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.319288988058466</v>
+        <v>0.3121957699504857</v>
       </c>
       <c r="C2" t="n">
-        <v>4.80467326458389</v>
+        <v>3.300635781677776</v>
       </c>
       <c r="D2" t="n">
-        <v>19.2049485904761</v>
+        <v>7.141232800691299</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.8047553800419</v>
+        <v>2.896155727528091</v>
       </c>
       <c r="C3" t="n">
-        <v>19.88039101099791</v>
+        <v>25.80523840612741</v>
       </c>
       <c r="D3" t="n">
-        <v>68.69779560467056</v>
+        <v>50.49128442941346</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.47807974090174</v>
+        <v>11.8182788637231</v>
       </c>
       <c r="C4" t="n">
-        <v>75.68293052038661</v>
+        <v>71.76477543273759</v>
       </c>
       <c r="D4" t="n">
-        <v>136.727021022749</v>
+        <v>107.8322225913569</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.4385320952914</v>
+        <v>18.01507037292897</v>
       </c>
       <c r="C5" t="n">
-        <v>173.7693436516855</v>
+        <v>182.6541603751191</v>
       </c>
       <c r="D5" t="n">
-        <v>129.2470852640926</v>
+        <v>107.0104997629024</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.79129831628549</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>228.7501603326196</v>
+        <v>280.554041442611</v>
       </c>
       <c r="D6" t="n">
-        <v>71.92970904705108</v>
+        <v>65.56994741894023</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.87668500435917</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="C7" t="n">
-        <v>180.1389227568388</v>
+        <v>182.7739335950372</v>
       </c>
       <c r="D7" t="n">
-        <v>40.72289477215769</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>127.1755976081318</v>
+        <v>69.76299186377835</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>63.45624461169682</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>17.50947030524187</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.530945581548277</v>
+        <v>0.3259402378099411</v>
       </c>
       <c r="C2" t="n">
-        <v>2.692933952749001</v>
+        <v>10.69515949006475</v>
       </c>
       <c r="D2" t="n">
-        <v>13.99874051485527</v>
+        <v>7.080364443027996</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.48921345635117</v>
+        <v>1.904590546238812</v>
       </c>
       <c r="C3" t="n">
-        <v>19.71840263979719</v>
+        <v>18.17705874412969</v>
       </c>
       <c r="D3" t="n">
-        <v>69.0070461315083</v>
+        <v>44.68915549731481</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.28365263773187</v>
+        <v>8.653124265231385</v>
       </c>
       <c r="C4" t="n">
-        <v>66.14917856444583</v>
+        <v>67.70623042338129</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5092940165845</v>
+        <v>108.8277147634632</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.91177554646737</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C5" t="n">
-        <v>164.5900026169778</v>
+        <v>157.0305452942773</v>
       </c>
       <c r="D5" t="n">
-        <v>143.1879026643973</v>
+        <v>121.0985793188441</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.44540432922113</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="C6" t="n">
-        <v>258.8986505823349</v>
+        <v>286.9943063824701</v>
       </c>
       <c r="D6" t="n">
-        <v>84.56872899152451</v>
+        <v>82.59639785369266</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.15804568485051</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>231.4617474917492</v>
+        <v>299.4330497952772</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>162.8081305337698</v>
+        <v>155.5481062608646</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>75.32655610374501</v>
+        <v>57.13280764864312</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>22.63124807829746</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.799764526062656</v>
+        <v>0.4977460860531329</v>
       </c>
       <c r="C2" t="n">
-        <v>4.637776154861932</v>
+        <v>10.86205659978671</v>
       </c>
       <c r="D2" t="n">
-        <v>15.10124318672444</v>
+        <v>6.320491719940965</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.08393158094649</v>
+        <v>1.482439033412684</v>
       </c>
       <c r="C3" t="n">
-        <v>15.17291076913446</v>
+        <v>30.62071089545801</v>
       </c>
       <c r="D3" t="n">
-        <v>65.26658737832796</v>
+        <v>40.2761995667254</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.80019079888594</v>
+        <v>6.151631114810514</v>
       </c>
       <c r="C4" t="n">
-        <v>58.19800390775092</v>
+        <v>56.0793923619863</v>
       </c>
       <c r="D4" t="n">
-        <v>139.6752093786022</v>
+        <v>106.7856795386298</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.68459091615885</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="C5" t="n">
-        <v>145.3722913063465</v>
+        <v>140.8807955594173</v>
       </c>
       <c r="D5" t="n">
-        <v>156.834195753428</v>
+        <v>131.7996292951343</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.79007988886977</v>
+        <v>20.97111271041612</v>
       </c>
       <c r="C6" t="n">
-        <v>261.0319883436633</v>
+        <v>267.713763218767</v>
       </c>
       <c r="D6" t="n">
-        <v>103.648013875857</v>
+        <v>98.49580192396976</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.22572952318131</v>
+        <v>13.53437385074653</v>
       </c>
       <c r="C7" t="n">
-        <v>293.863595069085</v>
+        <v>358.0620409451924</v>
       </c>
       <c r="D7" t="n">
-        <v>55.57477404200344</v>
+        <v>55.63466065196249</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>220.6379790524282</v>
+        <v>270.8740090787374</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>124.3609269400562</v>
+        <v>120.1453022980204</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>54.09429850399926</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.748533718992575</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C2" t="n">
-        <v>7.192283681312134</v>
+        <v>7.797040267128168</v>
       </c>
       <c r="D2" t="n">
-        <v>9.433613690107601</v>
+        <v>16.26559596396115</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.39488356128547</v>
+        <v>0.8717919613711677</v>
       </c>
       <c r="C2" t="n">
-        <v>2.59770442543706</v>
+        <v>21.72411319957342</v>
       </c>
       <c r="D2" t="n">
-        <v>11.11534750748239</v>
+        <v>7.668431317871836</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.61469723604552</v>
+        <v>1.546252634188726</v>
       </c>
       <c r="C3" t="n">
-        <v>18.38322576202152</v>
+        <v>35.99577957620931</v>
       </c>
       <c r="D3" t="n">
-        <v>70.57784245830321</v>
+        <v>36.52101459798134</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.78813208899449</v>
+        <v>4.518002934943822</v>
       </c>
       <c r="C4" t="n">
-        <v>82.90663012823464</v>
+        <v>65.52380527684062</v>
       </c>
       <c r="D4" t="n">
-        <v>144.8313483213065</v>
+        <v>103.2121178951714</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.06159773012285</v>
+        <v>13.25359400733194</v>
       </c>
       <c r="C5" t="n">
-        <v>217.947990342792</v>
+        <v>122.3257639491526</v>
       </c>
       <c r="D5" t="n">
-        <v>145.3722913063465</v>
+        <v>137.1010668980671</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.35225180384214</v>
+        <v>21.29312595740907</v>
       </c>
       <c r="C6" t="n">
-        <v>249.8420280106581</v>
+        <v>249.7615246989099</v>
       </c>
       <c r="D6" t="n">
-        <v>82.2341329508256</v>
+        <v>114.113444403128</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.60559946480004</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>155.1662064039126</v>
+        <v>370.9376620863893</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>66.95322993422397</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>91.6265132373548</v>
+        <v>362.3336252063702</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>41.26874649571891</v>
+        <v>211.7796695170091</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>23.48831382410494</v>
+        <v>83.98851609831463</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.86995163914969</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.857507714163971</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C2" t="n">
-        <v>4.977460860531329</v>
+        <v>13.38416645199677</v>
       </c>
       <c r="D2" t="n">
-        <v>12.01462840457247</v>
+        <v>21.15960826963151</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.33351648200343</v>
+        <v>6.435356201337843</v>
       </c>
       <c r="C3" t="n">
-        <v>18.12306262039612</v>
+        <v>15.39380400258999</v>
       </c>
       <c r="D3" t="n">
-        <v>11.05938788834032</v>
+        <v>14.08317081742049</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39798914775357</v>
+        <v>11.67754411689905</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14241377353342</v>
+        <v>59.94472646674844</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576234017382773</v>
+        <v>0.7785029411266031</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.751078051477815</v>
+        <v>2.783254741539707</v>
       </c>
       <c r="C2" t="n">
-        <v>4.231332605303753</v>
+        <v>5.91895690890402</v>
       </c>
       <c r="D2" t="n">
-        <v>27.32694734770996</v>
+        <v>17.94242104281471</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96874830438012</v>
+        <v>14.16171063376024</v>
       </c>
       <c r="C3" t="n">
-        <v>18.9280957378785</v>
+        <v>39.96694903988765</v>
       </c>
       <c r="D3" t="n">
-        <v>18.47649179392497</v>
+        <v>29.1628155546515</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.61706164208151</v>
+        <v>8.066039138091794</v>
       </c>
       <c r="C4" t="n">
-        <v>28.15456066239003</v>
+        <v>25.58925391119311</v>
       </c>
       <c r="D4" t="n">
-        <v>20.86704745376596</v>
+        <v>21.72214970416493</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.105088062083415</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44141430078881</v>
+        <v>13.62679132919116</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14683767808492</v>
+        <v>73.7449883697404</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25082406332396</v>
+        <v>1.603151921081313</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.205226327916588</v>
+        <v>1.73278469799562</v>
       </c>
       <c r="C2" t="n">
-        <v>2.530945581548277</v>
+        <v>5.482079180514189</v>
       </c>
       <c r="D2" t="n">
-        <v>27.04224051347839</v>
+        <v>14.68596390782804</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.94420461177396</v>
+        <v>11.57971417159113</v>
       </c>
       <c r="C3" t="n">
-        <v>17.43583922742335</v>
+        <v>29.25608158655495</v>
       </c>
       <c r="D3" t="n">
-        <v>36.04977569994288</v>
+        <v>37.18860303686917</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.17557827480671</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="C4" t="n">
-        <v>39.48785616021521</v>
+        <v>71.67543639165113</v>
       </c>
       <c r="D4" t="n">
-        <v>25.44886398948582</v>
+        <v>31.95785126864217</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.33351648200343</v>
+        <v>7.780350556155974</v>
       </c>
       <c r="C5" t="n">
-        <v>31.95588777323368</v>
+        <v>30.38509144643879</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94330497952772</v>
+        <v>27.75891633757857</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.997496725243765</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.60879105428681</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73395580921335</v>
+        <v>14.83452388780549</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0771304362014</v>
+        <v>87.35886289485457</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020186742764006</v>
+        <v>2.472420647967582</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.049128442941345</v>
+        <v>2.263910205993145</v>
       </c>
       <c r="C2" t="n">
-        <v>3.274128593663113</v>
+        <v>5.413356841216912</v>
       </c>
       <c r="D2" t="n">
-        <v>21.34712208114264</v>
+        <v>16.83402788472006</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.79065105928395</v>
+        <v>8.423395302437633</v>
       </c>
       <c r="C3" t="n">
-        <v>13.03270077387641</v>
+        <v>24.45042657426681</v>
       </c>
       <c r="D3" t="n">
-        <v>48.58178514465342</v>
+        <v>40.30565199785281</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.43381897875263</v>
+        <v>21.31374265919825</v>
       </c>
       <c r="C4" t="n">
-        <v>41.79790850830795</v>
+        <v>72.6709285637574</v>
       </c>
       <c r="D4" t="n">
-        <v>37.12675293150163</v>
+        <v>43.40601124786423</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.91246989006857</v>
+        <v>19.38951715887451</v>
       </c>
       <c r="C5" t="n">
-        <v>53.77523050011905</v>
+        <v>88.52909923045614</v>
       </c>
       <c r="D5" t="n">
-        <v>32.00497515844602</v>
+        <v>32.79037332184348</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.7597749120958</v>
+        <v>7.728317927830893</v>
       </c>
       <c r="C6" t="n">
-        <v>32.52333794628834</v>
+        <v>31.15478164656829</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>33.97239755775664</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05938714664659</v>
+        <v>16.07346783959611</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8160018614563</v>
+        <v>100.6706669953651</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879766532055842</v>
+        <v>3.383887966230759</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.521349088684061</v>
+        <v>2.882411259668635</v>
       </c>
       <c r="C2" t="n">
-        <v>4.963716392671873</v>
+        <v>11.70635962543897</v>
       </c>
       <c r="D2" t="n">
-        <v>19.48867367700343</v>
+        <v>19.94911335029519</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96812640957437</v>
+        <v>8.128870991163589</v>
       </c>
       <c r="C3" t="n">
-        <v>12.07058802371454</v>
+        <v>22.45256999612455</v>
       </c>
       <c r="D3" t="n">
-        <v>50.80544369477244</v>
+        <v>44.13446804441536</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.69135567243478</v>
+        <v>18.56975782582842</v>
       </c>
       <c r="C4" t="n">
-        <v>30.33698580893068</v>
+        <v>66.26404304584271</v>
       </c>
       <c r="D4" t="n">
-        <v>45.32041927114551</v>
+        <v>53.27159392784043</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.74004214701963</v>
+        <v>25.9181393921158</v>
       </c>
       <c r="C5" t="n">
-        <v>49.5291716792516</v>
+        <v>113.2200539922634</v>
       </c>
       <c r="D5" t="n">
-        <v>30.97414006898687</v>
+        <v>40.22711218151306</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.36984114706057</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C6" t="n">
-        <v>40.57366912111219</v>
+        <v>87.7083581497058</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>22.21793229480956</v>
+        <v>31.50035683846316</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059385680006153</v>
+        <v>17.33739691758213</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18174075005768</v>
+        <v>114.426819656042</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294539260004615</v>
+        <v>4.334349229395531</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.873395603881167</v>
+        <v>3.371321616383547</v>
       </c>
       <c r="C2" t="n">
-        <v>7.895215037552849</v>
+        <v>13.3723854795458</v>
       </c>
       <c r="D2" t="n">
-        <v>14.66829244915159</v>
+        <v>24.23247858392402</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.18196748265093</v>
+        <v>8.948630324209677</v>
       </c>
       <c r="C3" t="n">
-        <v>16.87624303600267</v>
+        <v>34.69496386808228</v>
       </c>
       <c r="D3" t="n">
-        <v>55.18894719423445</v>
+        <v>49.10211142790422</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.5967480399286</v>
+        <v>17.08928228782423</v>
       </c>
       <c r="C4" t="n">
-        <v>30.33698580893068</v>
+        <v>60.30385273336033</v>
       </c>
       <c r="D4" t="n">
-        <v>62.25654891710723</v>
+        <v>62.26931163726244</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.30579086657305</v>
+        <v>26.89988709636261</v>
       </c>
       <c r="C5" t="n">
-        <v>53.72614311490671</v>
+        <v>117.8097245096173</v>
       </c>
       <c r="D5" t="n">
-        <v>41.35612204139689</v>
+        <v>48.76831720846032</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.47929816831747</v>
+        <v>25.51954982419159</v>
       </c>
       <c r="C6" t="n">
-        <v>63.07434475474484</v>
+        <v>132.8707160404676</v>
       </c>
       <c r="D6" t="n">
-        <v>34.09315252537899</v>
+        <v>41.13719230334986</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.57618809140164</v>
+        <v>13.53437385074653</v>
       </c>
       <c r="C7" t="n">
-        <v>44.25620475974196</v>
+        <v>76.77463396750906</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>33.46287049925253</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285423968959598</v>
+        <v>17.73243095770383</v>
       </c>
       <c r="C21" t="n">
-        <v>76.49695167407577</v>
+        <v>127.6735028954676</v>
       </c>
       <c r="D21" t="n">
-        <v>6.374745972839648</v>
+        <v>5.319729287311149</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.114324702049134</v>
+        <v>2.986476516318797</v>
       </c>
       <c r="C2" t="n">
-        <v>6.957645979997145</v>
+        <v>8.343873738393642</v>
       </c>
       <c r="D2" t="n">
-        <v>18.5147799543906</v>
+        <v>19.18629538409542</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48983535115693</v>
+        <v>11.77115497391926</v>
       </c>
       <c r="C3" t="n">
-        <v>25.42726553999239</v>
+        <v>53.08800710714627</v>
       </c>
       <c r="D3" t="n">
-        <v>54.11884219660542</v>
+        <v>54.80115685105696</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.99163160121406</v>
+        <v>12.91587279707104</v>
       </c>
       <c r="C4" t="n">
-        <v>37.20332925243288</v>
+        <v>95.8607910857713</v>
       </c>
       <c r="D4" t="n">
-        <v>75.35109979635119</v>
+        <v>59.47427592327178</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.05530633326987</v>
+        <v>14.35806017460961</v>
       </c>
       <c r="C5" t="n">
-        <v>55.19876467127693</v>
+        <v>79.37430188835464</v>
       </c>
       <c r="D5" t="n">
-        <v>55.12513359345841</v>
+        <v>38.60722846950583</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.4277485660779</v>
+        <v>8.372344421816802</v>
       </c>
       <c r="C6" t="n">
-        <v>75.99512629033711</v>
+        <v>50.55607977789376</v>
       </c>
       <c r="D6" t="n">
-        <v>39.40637110076273</v>
+        <v>26.04282135055514</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>70.90574619152163</v>
+        <v>23.47555110394973</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>26.76931465169778</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>44.2277340763188</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.49991487010665</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.501406726630605</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.26617735625194</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.501406726630605</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
